--- a/ASSET-MANAGEMENT-SOFTWARE-master/DB_AM_OCP_SYNTHETIC_2026/00_data_dictionary.xlsx
+++ b/ASSET-MANAGEMENT-SOFTWARE-master/DB_AM_OCP_SYNTHETIC_2026/00_data_dictionary.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog Codes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Mapping" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Index" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Glossary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8440,4 +8441,6354 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G171"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>field_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sap_field</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description_es</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>description_en</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>data_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>used_in_templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>equipment_tag</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EQUNR (alias)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tag tecnico del equipo (formato OCP)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Technical equipment tag (OCP format)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OCP-CON1-MSAG01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>01-30 (todos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>equnr</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EQUNR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Numero de equipo SAP (12 digitos)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SAP Equipment Number (12 digits)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>000000100001</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>01, 02, 06, 23, 24, 26, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eqktx</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EQKTX</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Texto corto / descripcion del equipo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Equipment Short Text / Description</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>String(40)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Molino SAG 40x22 L1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01, 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eqart</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EQART</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tipo de equipo SAP (M=Maquina, Q=Inspeccion)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SAP Equipment Type (M=Machine, Q=Inspection)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>String(1)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>eqart_desc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Descripcion del tipo de equipo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Equipment type description</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Maquinas</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sap_func_loc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TPLNR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ubicacion tecnica SAP (jerarquia)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SAP Functional Location (hierarchy)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>String(40)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>02-01-01-CHAN01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>01-30 (todos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tplnr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TPLNR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ubicacion tecnica SAP (nombre original SAP)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SAP Technical Place Number</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>String(40)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>02-01-01-CHAN01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>fl_type</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FLTYP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tipo de ubicacion tecnica (M=estandar)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Functional Location Type (M=standard)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>String(1)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pltxt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PLTXT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Texto descriptivo de la ubicacion tecnica</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Functional Location Description Text</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>String(40)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Chancado Primario</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nivel jerarquico (1=Planta, 2=Area, 3=Sistema, 4=Equipo)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hierarchy Level (1=Plant to 4=Equipment)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>parent_fl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TPLMA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ubicacion tecnica padre (jerarquia superior)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Parent Functional Location</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>String(40)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>02-01-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>herst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HERST</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fabricante del equipo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Equipment Manufacturer</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>String(30)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Metso</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Modelo del equipo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Equipment Model</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>C160</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>power_kw</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Potencia nominal del equipo (kW)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rated Power (kW)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>weight_kg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Peso del equipo (kg)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Equipment Weight (kg)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>120000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>abckz</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ABCKZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Indicador criticidad ABC (1=Alto, 2=Medio, 3=Bajo)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ABC Criticality Indicator (1=High, 2=Med, 3=Low)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>String(1)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>01, 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>abckz_desc</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Descripcion del nivel de criticidad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Criticality level description</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01, 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>STAT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Estado del equipo (ACTIVO, INACTIVO)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Equipment Status</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>install_date</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>INBDT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fecha de instalacion del equipo</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Equipment Installation Date</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2020-03-15</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>serial_number</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SERNR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Numero de serie del equipo</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Equipment Serial Number</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>String(30)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SN-2020-001234</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aufnr</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AUFNR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Numero de orden de trabajo SAP</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SAP Work Order Number</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>06, 23, 26, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>auart</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AUART</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tipo de orden (PM01/PM02/PM03/PM06/PM07)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Order Type</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>String(4)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PM01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>06, 23, 26, 27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>auart_desc</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Descripcion del tipo de orden</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Order Type Description</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Orden Mant. de Averia</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>06, 23, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>erdat</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ERDAT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Fecha de creacion de la orden</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Order Created Date</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gstrp</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GSTRP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fecha inicio planificada (basica)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Basic Start Date (planned)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-01-20 08:00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gltrp</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GLTRP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fecha fin planificada (basica)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Basic End Date (planned)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-01-20 16:00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>iedd</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IEDD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fecha inicio real de la orden</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Actual Start Date</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-01-20 09:00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>iedt</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IEDT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fecha fin real de la orden</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Actual End Date</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-01-20 15:30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>duration_hours</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Duracion total de la intervencion (horas)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Total intervention duration (hours)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>system_status</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>STAT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Status sistema SAP de la orden (ABIE/LIBE/NOTI/CTEC)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SAP System Status of Order</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CTEC</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>06, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KTEXT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Texto corto de la orden/aviso (max 72 chars SAP)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Short Text (max 72 chars SAP limit)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>String(72)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Reparar fuga aceite Sist Lubricacion</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>06, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>failure_found</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hallazgo al intervenir (que se encontro)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Finding during intervention (what was found)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rodamiento colapsado</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cause_description</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Descripcion de la causa raiz</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Root cause description</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Desgaste normal por horas operacion</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>solution_description</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Accion correctiva ejecutada</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Corrective action taken</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Se reemplazo componente danado</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>closure_comments</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Notas de cierre y recomendaciones</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closure notes and recommendations</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Equipo entregado operativo</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>crew_size</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cantidad de trabajadores asignados</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Number of workers assigned</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>specialty</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Especialidad del puesto trabajo (MEC/ELE/INS/LUB/SOL)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Work Center specialty</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>String(3)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>MEC</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>06, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>synth_trace_id</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ID trazabilidad datos sinteticos (interno)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Synthetic data trace ID (internal)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S26-OT-0001-A1B2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>priokx</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PRIOKX</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Codigo prioridad SAP clase Z1 (I/A/M/B)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SAP Priority Code class Z1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>String(1)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>priokx_desc</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Descripcion de la prioridad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Priority description</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Alta (2-6 dias)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>priority_class</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Clase de prioridad SAP</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SAP Priority Class</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>String(2)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Z1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>06, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Codigo prioridad (I/A/M/B o status backlog)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Priority code</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>priority_desc</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Descripcion de la prioridad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Priority description</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Alta (2-6 dias)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ilart</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ILART</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tipo de aviso/notificacion SAP (A1/A2/A3)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SAP Notification Type (linked to order)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>String(2)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ilart_desc</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Descripcion del tipo de aviso</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Notification Type description</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Aviso de mantenimiento</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>qmnum</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>QMNUM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Numero de notificacion/aviso SAP</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SAP Notification Number</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>5000001</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>06, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>qmart</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>QMART</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Clase de aviso SAP (A1/A2/A3)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SAP Notification Class</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>String(2)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>qmart_desc</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Descripcion de la clase de aviso</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Notification Class description</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Aviso de mantenimiento</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>notification_catalog</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Catalogo de aviso asignado (M001-M003, P001-P002)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Assigned notification catalog</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>06, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>notification_status_schema</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Esquema status usuario del aviso (ZPM00001)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Notification user status schema</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ZPM00001</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>notif_user_status</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Status usuario del aviso (APRO/RECH)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Notification user status</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>String(4)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>APRO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>user_status_schema</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Esquema status usuario (ZPM00001)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>User status schema</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ZPM00001</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>user_status</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Status usuario (APRO=Aprobado, RECH=Rechazado)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>User status</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>String(4)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>APRO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>reported_by</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ID del trabajador que reporto</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Reporting worker ID</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>W-MEC-001</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>reported_date</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fecha en que se reporto el aviso</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Notification reported date</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>long_text</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Texto largo del aviso (descripcion extendida)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Notification long text (extended description)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Detalle: vibracion excesiva...</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>damage_code</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Codigo de dano (catalogo B de template 15)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Damage code (catalog B from template 15)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>B-ROD</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cause_code</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Codigo de causa (catalogo 5 de template 15)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Cause code (catalog 5 from template 15)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>5-FLB</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>object_part_code</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Codigo parte objeto (catalogo B)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Object part code (catalog B)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>B-MOT</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>linked_order</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Numero de orden vinculada al aviso</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Linked order number</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1900001</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>completed_date</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Fecha completado (avisos cerrados)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Completion date (closed notifications)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>arbpl</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ARBPL</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Puesto de trabajo SAP (8 caracteres)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SAP Work Center (8 characters)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>String(8)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PASMEC01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>supervisor_wc</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Puesto de trabajo del supervisor</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Supervisor Work Center</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>String(8)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SPASMEC</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>06, 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>work_center</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ARBPL</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Puesto de trabajo responsable</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Responsible Work Center</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>String(8)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>PASMEC01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>23-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>planning_group</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>INGRP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Grupo de planificacion (P01/P02/P03)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Planning Group</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>String(3)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>06, 12, 13, 23-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>planning_center</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>IWERK</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Centro de planificacion SAP</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SAP Planning Center</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>String(4)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>AN01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>06, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>business_area</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GSBER</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Area de empresa (SEC/RIP/HUM)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Business Area</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>String(3)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>06, 23, 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Nombre del area de proceso</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Process area name</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Chancado</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>01-30 (todos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>subprocess</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Nombre del subproceso</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sub-process name</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Chancado Primario</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cost_labour_usd</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Costo mano de obra interna (USD)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Internal labour cost (USD)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2340.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cost_materials_usd</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Costo materiales y repuestos (USD)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Materials &amp; spare parts cost (USD)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>5600.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cost_external_usd</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Costo servicios externos (USD)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>External services cost (USD)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>12000.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>value_cat_labour</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Categoria valor mano obra (ZMANT001)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Labour value category</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ZMANT001</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>value_cat_materials</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Categoria valor materiales (ZMANT002)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Materials value category</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ZMANT002</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>value_cat_external</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Categoria valor servicios ext. (ZMANT003)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>External services value category</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ZMANT003</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>value_category</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Categoria de valor (ZMANT001/002/003)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Value category</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ZMANT001</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>amount_usd</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Monto en dolares</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Amount in USD</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cost_center</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Centro de costo SAP</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SAP Cost Center</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CC-PL-MEC-SEC</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>wbs_element</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Elemento PEP/WBS del proyecto</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>WBS / PEP Element</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>WBS-PL-SEC-MNT-2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cost_element</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Elemento de costo SAP (cuenta CO)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SAP Cost Element (CO account)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>621000</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>budget_usd</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Presupuesto asignado (USD)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Assigned budget (USD)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>45000.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>variance_usd</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Varianza costo vs presupuesto (USD)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Cost vs budget variance (USD)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-2300.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>variance_pct</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Varianza porcentual (%)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Variance percentage (%)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-5.1</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>unit_cost_usd</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Costo unitario del material (USD)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Unit cost of material (USD)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1250.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>total_cost_usd</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Costo total (cantidad x unitario)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Total cost (qty x unit cost)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>3750.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>material_code</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MATNR (alias)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Codigo material sintetico (S26-MAT-NNNN)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Synthetic material code</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S26-MAT-0001</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>07, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>sap_material_number</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MATNR</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Numero de material SAP (12 digitos)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SAP Material Number (12 digits)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>String(12)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>000000010001</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>component_desc</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Descripcion del componente/material</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Component/Material description</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Rodamiento SKF 22328</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Cantidad (en la unidad de medida)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Quantity (in unit of measure)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>unit_of_measure</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MEINS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Unidad de medida (EA/KG/L/M/DR/PL/BX/MT)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Unit of Measure</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>String(3)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>07, 25, 27, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>item_number</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Numero posicion BOM (incrementos de 10)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BOM Item Number (increments of 10)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>String(4)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>item_category</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Categoria del item (SPARE/WEAR/CONSUMABLE)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Item category</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>SPARE</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>critical_spare</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Es repuesto critico (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Is critical spare (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>component_category</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Categoria componente BOM (L=stock/N=non-stock/D=doc)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BOM Component Category</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>String(1)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>movement_type</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BWART</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Tipo de movimiento SAP (261/262/101/311)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SAP Movement Type</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>String(3)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>storage_location</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>LGORT</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ubicacion almacenamiento</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Storage Location</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ALM-CENTRAL</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>reservation_id</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Numero de reserva de material</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Material reservation number</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S26-RES-0001</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>movement_doc_id</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Numero documento movimiento</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Movement document number</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S26-MOV-0001</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>lead_time_days</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tiempo de entrega (dias)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lead time (days)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>07, 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>measurement_point_id</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>POINT</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ID punto de medida SAP (12 digitos)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SAP Measurement Point ID (12 digits)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>String(12)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>000000000001</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>04, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>measurement_doc_id</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ID documento de medicion</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Measurement document ID</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S26-MDOC-0001</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>characteristic</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ATNAM</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Caracteristica medida (TEMP_BRG_DE, VIB_RAD_DE...)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Measured characteristic</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>TEMP_BRG_DE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>04, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>characteristic_desc</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Descripcion de la caracteristica medida</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Characteristic description</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Temperatura rodamiento LA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>reading_date</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Fecha de la lectura/medicion</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Reading/measurement date</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>reading_time</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Hora de la lectura (turno 08:00-20:00)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Reading time (shift 08:00-20:00)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>measured_value</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Valor medido</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Measured value</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>counter_reading</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Lectura del contador (horometro, ciclos)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Counter reading (hours, cycles)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>45230</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>valuation_code</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Codigo valoracion (1=OK, 2=Warning, 3=Alarm)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Valuation code (1=OK, 2=Warning, 3=Alarm)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>lower_limit</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Limite inferior de medicion</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Lower measurement limit</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>04, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>upper_limit</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Limite superior de medicion</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Upper measurement limit</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>04, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>target_value</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Valor objetivo de medicion</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Target measurement value</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>04, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>is_counter</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Es tipo contador (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Is counter type (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>04, 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>confirmation_id</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ID de confirmacion de tiempo</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Time confirmation ID</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S26-CONF-0001</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>operation_number</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>VORNR</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Numero de operacion (0010, 0020, 0030...)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Operation Number (increments of 10)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>String(4)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>sub_operation</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Sub-operacion (0000 por defecto)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sub-operation (0000 default)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>String(4)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0000</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>confirmation_type</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Tipo confirmacion (INDIVIDUAL/COLLECTIVE)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Confirmation type</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>INDIVIDUAL</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>worker_id</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ID del trabajador que ejecuto</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Executing worker ID</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>W-MEC-001</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>09, 25, 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>worker_name</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Nombre del trabajador</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Worker name</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Tecnico MEC 001</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>actual_work_hours</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Horas netas trabajadas</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Actual net work hours</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>break_hours</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Horas de descanso (1h turno 7x7)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Break hours (1h per 7x7 shift)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>travel_time_hours</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tiempo de traslado al equipo (horas)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Travel time to equipment (hours)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>setup_time_hours</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tiempo de preparacion (horas)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Setup time (hours)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>total_duration_hours</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Duracion total (trabajo+descanso+traslado+prep)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Total duration (work+break+travel+setup)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>final_confirmation</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Es ultima confirmacion de la orden (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Is final confirmation for order (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>system_status_after</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Status sistema despues de confirmacion (PCNF/CNF)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>System status after confirmation</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>String(4)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>CNF</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ttf_record_id</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ID registro time-to-failure</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Time-to-failure record ID</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>S26-TTF-0001</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>failure_event_id</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ID del evento de falla (ref OT PM01)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Failure event ID (ref PM01 order)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>1000005</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>failure_date</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Fecha del evento de falla</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Failure event date</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>previous_failure_date</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Fecha falla previa en mismo equipo</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Previous failure date on same equipment</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>time_to_failure_days</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Dias entre fallas (TTF)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Days between failures (TTF)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>operating_hours</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Horas operacion entre fallas</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Operating hours between failures</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>suspension</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Dato censurado (TRUE=aun funcionando)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Censored data (TRUE=still running)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>failure_mechanism</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Mecanismo de falla (18 valores validos)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Failure mechanism (18 valid values)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>WEARS</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>03, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>failure_cause</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Causa de falla (44 valores validos)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Failure cause (44 valid values)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>ABRASION</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>03, 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>failure_pattern</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Patron falla Nowlan&amp;Heap (A-F)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Failure pattern Nowlan&amp;Heap (A-F)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>B_AGE</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>maintainable_item</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Item mantenible que fallo</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Maintainable item that failed</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Rodamiento</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>repair_duration_hours</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Duracion de la reparacion (horas)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Repair duration (hours)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Parametro forma Weibull (&gt;1=desgaste, &lt;1=infant, =1=aleatorio)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Weibull shape parameter</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>eta_days</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Parametro escala Weibull (vida caracteristica, dias)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Weibull scale parameter (characteristic life, days)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>180.5</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>gamma_days</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Parametro ubicacion Weibull (periodo libre falla, dias)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Weibull location parameter (failure-free period, days)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>r_squared</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Bondad de ajuste del modelo Weibull</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Weibull model goodness of fit</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>mtbf_days</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Tiempo medio entre fallas (dias)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Mean Time Between Failures (days)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>recommended_interval_days</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Intervalo optimo recomendado (dias)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Recommended optimal interval (days)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>equipment_class</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Clase de equipo para agrupacion (ej: BOMBA_PULPA)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Equipment class for grouping</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>BOMBA_PULPA</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>sample_size</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Tamano de muestra para calculo Weibull</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Sample size for Weibull calculation</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>confidence_level</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Nivel de confianza del calculo</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Calculation confidence level</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>backlog_id</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ID del item de backlog</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Backlog item ID</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>S26-BKL-0001</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>work_request_id</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ID de la solicitud de trabajo vinculada</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Linked work request ID</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>S26-WR-0001</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Estado del item (backlog, reserva, etc.)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Item status</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>AWAITING_MATERIALS</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>23, 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>blocking_reason</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Razon de bloqueo del item backlog</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Backlog item blocking reason</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Repuesto en transito</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>created_date</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Fecha de creacion del registro</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Record creation date</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>age_days</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Antiguedad del item en dias</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Item age in days</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>estimated_duration_hours</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Duracion estimada de la intervencion (horas)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Estimated intervention duration (hours)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>required_specialties</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Especialidades requeridas (CSV: MEC,ELE,INS)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Required specialties (CSV)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>MEC,ELE</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>materials_ready</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Materiales disponibles (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Materials available (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>shutdown_required</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Requiere parada de equipo (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Equipment shutdown required (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>groupable</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Agrupable en paquete de trabajo (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Groupable in work package (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>group_id</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ID del grupo/paquete de trabajo</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Work package group ID</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>WP-GRP-0005</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Periodo contable (YYYY-MM)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Accounting period</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>12, 13, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>recorded_by</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ID del tecnico que registro la lectura</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Recording technician ID</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>W-INS-003</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>posting_date</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Fecha de contabilizacion</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Posting date</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>27, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>settlement_rule</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Regla de liquidacion (FULL/PERIODIC)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Settlement rule</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>pm07_activity_class</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Clase actividad PM07 (RP1=Mayor, RP2=Menor)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>PM07 activity class (RP1=Major, RP2=Minor)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>String(3)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>RP1</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>pm07_activity_desc</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Descripcion clase actividad PM07</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>PM07 activity class description</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Reparacion Mayor</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>bom_id</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ID de lista de materiales</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Bill of Materials ID</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>S26-BOM-0001</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>bom_level</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Nivel de BOM (1=superior)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BOM level (1=top level)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>change_frequency</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Frecuencia de cambio (HIGH/MEDIUM/LOW)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Change frequency</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>applicable_system</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Sistema aplicable (LUBE/HIDR/TRAN/MECA/SELL/ELEC)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Applicable system</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>MECA</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Moneda (USD)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>String(3)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Texto libre / notas de la operacion</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Free text / operation notes</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Trabajo MEC en MSAG01</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>